--- a/vacios.xlsx
+++ b/vacios.xlsx
@@ -895,7 +895,7 @@
       <c r="F2" s="41" t="n"/>
       <c r="G2" s="40" t="inlineStr">
         <is>
-          <t>R7623BCL</t>
+          <t>R0755BDB</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>5979FKM</t>
+          <t>7450HDK</t>
         </is>
       </c>
     </row>
